--- a/data/employees/EMP018/AST-EMP018-06.xlsx
+++ b/data/employees/EMP018/AST-EMP018-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skills Matrix" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00048A81"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,17 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,215 +414,1883 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Skills Matrix - Jamie Brown (HR)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Narrative</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Author: Jamie Brown | Role: Manager | Location: Hsinchu | Date: 2025-01-31</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ast Emp018 06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>65</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ast Emp018 06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>82</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Employee ID</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Department</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Role</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Skills</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Last Review Date</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Rating</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ast Emp018 06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>91</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EMP006</t>
+          <t>EMP018</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Avery Wilson</t>
+          <t>Ast Emp018 06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>2026-W04</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Specialist</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Azure AI, Fabric</t>
-        </is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>94</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>4.2</v>
+          <t>Section 1: Automation backlog refinement. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EMP011</t>
+          <t>EMP018</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Alex Garcia</t>
+          <t>Ast Emp018 06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>2026-W05</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Lead</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Synapse, TypeScript</t>
-        </is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>80</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>3.9</v>
+          <t>Section 1: Fabric semantic model planning. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EMP016</t>
+          <t>EMP018</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Avery Wilson</t>
+          <t>Ast Emp018 06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>2026-W06</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Engineer</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Python, SQL</t>
-        </is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>67</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>4.5</v>
+          <t>Section 1: Operational risk review. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EMP021</t>
+          <t>EMP018</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Alex Garcia</t>
+          <t>Ast Emp018 06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>2026-W07</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>61</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ast Emp018 06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>68</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ast Emp018 06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>68</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ast Emp018 06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>64</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ast Emp018 06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>60</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ast Emp018 06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>80</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ast Emp018 06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>65</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ast Emp018 06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>61</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ast Emp018 06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>88</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ast Emp018 06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>77</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ast Emp018 06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>81</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ast Emp018 06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>63</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ast Emp018 06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>69</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ast Emp018 06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>64</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ast Emp018 06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>99</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ast Emp018 06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>73</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ast Emp018 06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>63</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ast Emp018 06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>86</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ontology, MLOps</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>4</v>
+          <t>Section 1: Fabric semantic model planning. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EMP018</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP018 contributes to ast emp018 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>